--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-17.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-05-17.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Var_C_Hybrid" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Var_B_Polozkovy_Dum" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Var_B_Polozkovy_Sklad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Var_D_PerPodlazi_Mistnost" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$17</definedName>
@@ -30,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;Kč&quot;;-#,##0 &quot;Kč&quot;;&quot;—&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,6 +88,16 @@
     <font>
       <b val="1"/>
       <color rgb="00A04000"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3A5F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="5">
@@ -207,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -254,6 +265,18 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3215,7 +3238,7 @@
         </is>
       </c>
       <c r="F34" s="22" t="n">
-        <v>75.8</v>
+        <v>76.05</v>
       </c>
       <c r="G34" s="10" t="n"/>
       <c r="H34" s="10" t="n"/>
@@ -3975,7 +3998,7 @@
         </is>
       </c>
       <c r="F53" s="22" t="n">
-        <v>100</v>
+        <v>59.5</v>
       </c>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
@@ -5495,7 +5518,7 @@
         </is>
       </c>
       <c r="F91" s="22" t="n">
-        <v>265.6584273084518</v>
+        <v>293.15</v>
       </c>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
@@ -5535,7 +5558,7 @@
         </is>
       </c>
       <c r="F92" s="22" t="n">
-        <v>265.6584273084518</v>
+        <v>293.15</v>
       </c>
       <c r="G92" s="10" t="n"/>
       <c r="H92" s="10" t="n"/>
@@ -5575,7 +5598,7 @@
         </is>
       </c>
       <c r="F93" s="22" t="n">
-        <v>14.3</v>
+        <v>14.35</v>
       </c>
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="n"/>
@@ -5615,7 +5638,7 @@
         </is>
       </c>
       <c r="F94" s="22" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
@@ -5695,7 +5718,7 @@
         </is>
       </c>
       <c r="F96" s="22" t="n">
-        <v>280.0584273084518</v>
+        <v>307.55</v>
       </c>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
@@ -7588,7 +7611,7 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>75.8</v>
+        <v>76.05</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
@@ -7598,7 +7621,7 @@
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -7607,7 +7630,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 + ARS — nástavba 3.NP</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ statika dům §4 + ARS — nástavba 3.NP</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -8228,7 +8251,7 @@
         </is>
       </c>
       <c r="K32" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
@@ -8237,7 +8260,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>TZ statika dům §4 — trapéz 40S/160 nad IPE180</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ statika dům §4 — trapéz 40S/160 nad IPE180</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -8291,7 +8314,7 @@
         </is>
       </c>
       <c r="K33" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
@@ -8300,7 +8323,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>TZ PBŘ + statika §4 — ochrana ocelobetonu</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ PBŘ + statika §4 — ochrana ocelobetonu</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -8596,7 +8619,7 @@
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>100</v>
+        <v>59.5</v>
       </c>
       <c r="H38" s="10" t="n"/>
       <c r="I38" s="10" t="n"/>
@@ -8606,7 +8629,7 @@
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
@@ -8615,7 +8638,7 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — minerální vata mezi trámy + protipož. SDK zespodu</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — minerální vata mezi trámy + protipož. SDK zespodu</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
@@ -10612,7 +10635,7 @@
         </is>
       </c>
       <c r="G70" s="22" t="n">
-        <v>265.6584273084518</v>
+        <v>293.15</v>
       </c>
       <c r="H70" s="10" t="n"/>
       <c r="I70" s="10" t="n"/>
@@ -10622,7 +10645,7 @@
         </is>
       </c>
       <c r="K70" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L70" s="20" t="inlineStr">
         <is>
@@ -10631,7 +10654,7 @@
       </c>
       <c r="M70" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — ETICS kontaktní, podklad existující omítka</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — ETICS kontaktní, podklad existující omítka</t>
         </is>
       </c>
       <c r="N70" s="20" t="inlineStr">
@@ -10675,7 +10698,7 @@
         </is>
       </c>
       <c r="G71" s="22" t="n">
-        <v>265.6584273084518</v>
+        <v>293.15</v>
       </c>
       <c r="H71" s="10" t="n"/>
       <c r="I71" s="10" t="n"/>
@@ -10685,7 +10708,7 @@
         </is>
       </c>
       <c r="K71" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L71" s="20" t="inlineStr">
         <is>
@@ -10694,7 +10717,7 @@
       </c>
       <c r="M71" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + PBŘ — EPS 70F grey 200 mm (h≤12m povoleno)</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 + PBŘ — EPS 70F grey 200 mm (h≤12m povoleno)</t>
         </is>
       </c>
       <c r="N71" s="20" t="inlineStr">
@@ -10738,7 +10761,7 @@
         </is>
       </c>
       <c r="G72" s="22" t="n">
-        <v>14.3</v>
+        <v>14.35</v>
       </c>
       <c r="H72" s="10" t="n"/>
       <c r="I72" s="10" t="n"/>
@@ -10748,7 +10771,7 @@
         </is>
       </c>
       <c r="K72" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L72" s="20" t="inlineStr">
         <is>
@@ -10757,7 +10780,7 @@
       </c>
       <c r="M72" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — sokl XPS + cihelný obklad</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — sokl XPS + cihelný obklad</t>
         </is>
       </c>
       <c r="N72" s="20" t="inlineStr">
@@ -10801,7 +10824,7 @@
         </is>
       </c>
       <c r="G73" s="22" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H73" s="10" t="n"/>
       <c r="I73" s="10" t="n"/>
@@ -10811,7 +10834,7 @@
         </is>
       </c>
       <c r="K73" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L73" s="20" t="inlineStr">
         <is>
@@ -10820,7 +10843,7 @@
       </c>
       <c r="M73" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS přesah na špaletách 35-40 mm</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — EPS přesah na špaletách 35-40 mm</t>
         </is>
       </c>
       <c r="N73" s="20" t="inlineStr">
@@ -10927,7 +10950,7 @@
         </is>
       </c>
       <c r="G75" s="22" t="n">
-        <v>280.0584273084518</v>
+        <v>307.55</v>
       </c>
       <c r="H75" s="10" t="n"/>
       <c r="I75" s="10" t="n"/>
@@ -10937,7 +10960,7 @@
         </is>
       </c>
       <c r="K75" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L75" s="20" t="inlineStr">
         <is>
@@ -10946,7 +10969,7 @@
       </c>
       <c r="M75" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — pastovitá probarvená lomená bílá</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — pastovitá probarvená lomená bílá</t>
         </is>
       </c>
       <c r="N75" s="20" t="inlineStr">
@@ -11179,7 +11202,7 @@
         </is>
       </c>
       <c r="G79" s="22" t="n">
-        <v>177.5</v>
+        <v>124</v>
       </c>
       <c r="H79" s="10" t="n"/>
       <c r="I79" s="10" t="n"/>
@@ -11189,7 +11212,7 @@
         </is>
       </c>
       <c r="K79" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L79" s="20" t="inlineStr">
         <is>
@@ -11198,7 +11221,7 @@
       </c>
       <c r="M79" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
         </is>
       </c>
       <c r="N79" s="20" t="inlineStr">
@@ -12250,7 +12273,7 @@
         </is>
       </c>
       <c r="G96" s="22" t="n">
-        <v>120.6</v>
+        <v>115.4</v>
       </c>
       <c r="H96" s="10" t="n"/>
       <c r="I96" s="10" t="n"/>
@@ -12260,7 +12283,7 @@
         </is>
       </c>
       <c r="K96" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L96" s="20" t="inlineStr">
         <is>
@@ -12269,7 +12292,7 @@
       </c>
       <c r="M96" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels (2× kuchyně, 3× koupelna, 7× chodba)</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 + DXF MTEXT room labels (2× kuchyně, 3× koupelna, 7× chodba)</t>
         </is>
       </c>
       <c r="N96" s="20" t="inlineStr">
@@ -12313,7 +12336,7 @@
         </is>
       </c>
       <c r="G97" s="22" t="n">
-        <v>54.8</v>
+        <v>102.1</v>
       </c>
       <c r="H97" s="10" t="n"/>
       <c r="I97" s="10" t="n"/>
@@ -12323,7 +12346,7 @@
         </is>
       </c>
       <c r="K97" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L97" s="20" t="inlineStr">
         <is>
@@ -12332,7 +12355,7 @@
       </c>
       <c r="M97" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 + DXF MTEXT room labels</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 + DXF MTEXT room labels</t>
         </is>
       </c>
       <c r="N97" s="20" t="inlineStr">
@@ -12439,7 +12462,7 @@
         </is>
       </c>
       <c r="G99" s="22" t="n">
-        <v>177.5</v>
+        <v>185.1</v>
       </c>
       <c r="H99" s="10" t="n"/>
       <c r="I99" s="10" t="n"/>
@@ -12449,7 +12472,7 @@
         </is>
       </c>
       <c r="K99" s="24" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="L99" s="20" t="inlineStr">
         <is>
@@ -12458,7 +12481,7 @@
       </c>
       <c r="M99" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — betonový potěr s kari + samonivelační stěrka</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — betonový potěr s kari + samonivelační stěrka</t>
         </is>
       </c>
       <c r="N99" s="20" t="inlineStr">
@@ -12502,7 +12525,7 @@
         </is>
       </c>
       <c r="G100" s="22" t="n">
-        <v>48.2</v>
+        <v>48.47</v>
       </c>
       <c r="H100" s="10" t="n"/>
       <c r="I100" s="10" t="n"/>
@@ -12512,7 +12535,7 @@
         </is>
       </c>
       <c r="K100" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L100" s="20" t="inlineStr">
         <is>
@@ -12521,7 +12544,7 @@
       </c>
       <c r="M100" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS — laminátové soklíky standard RD</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS — laminátové soklíky standard RD</t>
         </is>
       </c>
       <c r="N100" s="20" t="inlineStr">
@@ -13573,7 +13596,7 @@
         </is>
       </c>
       <c r="G117" s="22" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="H117" s="10" t="n"/>
       <c r="I117" s="10" t="n"/>
@@ -13583,7 +13606,7 @@
         </is>
       </c>
       <c r="K117" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L117" s="20" t="inlineStr">
         <is>
@@ -13592,7 +13615,7 @@
       </c>
       <c r="M117" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
         </is>
       </c>
       <c r="N117" s="20" t="inlineStr">
@@ -13636,7 +13659,7 @@
         </is>
       </c>
       <c r="G118" s="22" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="10" t="n"/>
@@ -13646,7 +13669,7 @@
         </is>
       </c>
       <c r="K118" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L118" s="20" t="inlineStr">
         <is>
@@ -13655,7 +13678,7 @@
       </c>
       <c r="M118" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
         </is>
       </c>
       <c r="N118" s="20" t="inlineStr">
@@ -17199,4 +17222,1984 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>VÝKAZ VÝMĚR — PER PODLAŽÍ + PER MÍSTNOST + AUDIT TRAIL (hk212-style)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="27" t="inlineStr">
+        <is>
+          <t>Per-místnost data z DXF tabulky místností (km_tabulka místností MTEXT); per-item formula audit trail ukazuje 'co s čím se sčítalo a násobilo'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ČÁST A — PER-MÍSTNOST z DXF (návrh fáze)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Č. místnosti</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Název místnosti</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Podlaží</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Plocha m²</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Skupina (vinyl/dlažba/sklep/biodeska)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Source DXF layer + MTEXT</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>vstup a chodba</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>chodba na zahradu</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>1.03</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>komora</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>dlazba</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>koupelna</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>dlazba</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>obývací místnost + kuchyně</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>24</v>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>dlazba</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>pokoj</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>schodiště do sklepa</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>schodiště</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>1.PP</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>dlazba_sklep</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>chodba</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>1.PP</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>dlazba_sklep</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>sklep 1</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>1.PP</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>dlazba_sklep</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>sklep 2</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>1.PP</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>dlazba_sklep</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>schodiště</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>2.NP</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>chodba</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>2.NP</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>koupelna</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>2.NP</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>dlazba</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>chodba</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>2.NP</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>společný pokoj</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>2.NP</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>pokoj</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>2.NP</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>pokoj</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>2.NP</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>3.01</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>schodiště</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>3.NP</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>chodba</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>3.NP</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>chodba</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>3.NP</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>3.04</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>koupelna</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>3.NP</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>dlazba</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>obývací místnost a kuchyně</t>
+        </is>
+      </c>
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>3.NP</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>dlazba</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>ložnice</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>3.NP</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>DXF km_tabulka místností MTEXT (embedded room table — návrh phase)</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>ČÁST B — PER-PODLAŽÍ SUBTOTAL z DXF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Podlaží</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Počet místností</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Σ Plocha m²</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Formula (jak vznikla)</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>1.NP</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" s="22" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>12.4 + 3.6 + 0.7 + 1.5 + 4.1 + 24.0 + 9.4 + 3.8 = 59.5 m²</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>1.PP</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>3.5 + 4.4 + 22.2 + 2.3 = 32.4 m²</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>2.NP</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="22" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>7.3 + 4.2 + 2.5 + 1.6 + 22.1 + 9.0 + 14.4 = 61.1 m²</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>3.NP</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="22" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>7.6 + 4.1 + 2.4 + 4.8 + 32.8 + 12.8 = 64.5 m²</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>CELKEM návrh</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="C38" s="29" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="D38" s="8">
+        <f> součet 4 podlaží | TZ baseline: 219.3 m² | Δ = -1.8 m² (-0.82 %)</f>
+        <v/>
+      </c>
+      <c r="E38" s="30" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ČÁST C — PER-MATERIAL podlaha z DXF (= cenotvorba PSV-77)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Σ Plocha m²</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Místnosti zahrnuté</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Audit trail (Σ formula)</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>1.01 vstup a chodba (12.4 m²); 1.02 chodba na zahradu (3.6 m²); 1.03 komora (0.7 m²); 1.07 pokoj (9.4 m²); 1.08 schodiště do sklepa (3.8 m²); 3.01 schodiště (7.6 m²); 3.02 chodba (4.1 m²); 3.03 chodba (2.4 m²); 3.06 ložnice (12.8 m²); 2.01 schodiště (7.3 m²); 2.02 chodba (4.2 m²); 2.04 chodba (1.6 m²); 2.05 společný pokoj (22.1 m²); 2.06 pokoj (9.0 m²); 2.07 pokoj (14.4 m²)</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>12.4 + 3.6 + 0.7 + 9.4 + 3.8 + 7.6 + 4.1 + 2.4 + 12.8 + 7.3 + 4.2 + 1.6 + 22.1 + 9.0 + 14.4 = 115.4 m²</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>dlazba</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>1.04 WC (1.5 m²); 1.05 koupelna (4.1 m²); 1.06 obývací místnost + kuchyně (24.0 m²); 3.04 koupelna (4.8 m²); 3.05 obývací místnost a kuchyně (32.8 m²); 2.03 koupelna (2.5 m²)</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>1.5 + 4.1 + 24.0 + 4.8 + 32.8 + 2.5 = 69.7 m²</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>dlazba_sklep</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>0.01 schodiště (3.5 m²); 0.02 chodba (4.4 m²); 0.03 sklep 1 (22.2 m²); 0.04 sklep 2 (2.3 m²)</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>3.5 + 4.4 + 22.2 + 2.3 = 32.4 m²</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>ČÁST D — POLOŽKY UPGRADED Z DXF EXTRAKCE (audit trail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Kapitola</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Položka</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>Nová qty</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Audit trail formula (co s čím se sčítalo / násobilo)</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>Conf před</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>Conf po</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="50" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV3.002</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>HSV-3 Svislé konstrukce</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Nadezdívka 3.NP Porotherm</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="n">
+        <v>76.05</v>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>obvod 41.0 m × výška 2.65 m × 0.7 (sníženo o štíty zachované) = 76.05 m²</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ statika dům §4 + ARS — nástavba 3.NP</t>
+        </is>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J48" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="50" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.005</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Trapéz 40S/160 dodávka</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E49" s="22" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="F49" s="8">
+        <f> zastavěná plocha 104.4 m² (TZ B m.1.j)</f>
+        <v/>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ statika dům §4 — trapéz 40S/160 nad IPE180</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J49" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="50" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.006</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Protipožární SDK podhled trapéz</t>
+        </is>
+      </c>
+      <c r="D50" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>104.4</v>
+      </c>
+      <c r="F50" s="8">
+        <f> zastavěná plocha 104.4 m² (TZ B m.1.j)</f>
+        <v/>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ PBŘ + statika §4 — ochrana ocelobetonu</t>
+        </is>
+      </c>
+      <c r="H50" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J50" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="50" customHeight="1">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV4.011</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>HSV-4 Vodorovné</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Strop 1.NP/2.NP — minerální vata mezi trámy</t>
+        </is>
+      </c>
+      <c r="D51" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>1.NP plocha (návrh) = 59.5 m² (DXF tabulka místností — strop 1.NP/2.NP)</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — minerální vata mezi trámy + protipož. SDK zespodu</t>
+        </is>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J51" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="50" customHeight="1">
+      <c r="A52" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.001</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Příprava podkladu</t>
+        </is>
+      </c>
+      <c r="D52" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="n">
+        <v>293.15</v>
+      </c>
+      <c r="F52" s="8">
+        <f> ETICS plocha = 293.15 m²</f>
+        <v/>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — ETICS kontaktní, podklad existující omítka</t>
+        </is>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J52" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="50" customHeight="1">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.002</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>ETICS EPS 70F grey 200 mm</t>
+        </is>
+      </c>
+      <c r="D53" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="n">
+        <v>293.15</v>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>obvod 41.0 m × 0.55 (volná fasáda, štíty zachované) × 13.0 m výška = 293.15 m²</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 + PBŘ — EPS 70F grey 200 mm (h≤12m povoleno)</t>
+        </is>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J53" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="50" customHeight="1">
+      <c r="A54" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.003</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>ETICS sokl XPS</t>
+        </is>
+      </c>
+      <c r="D54" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>obvod 41.0 m × 0.5 m výška sokl × 0.7 (řadovka) = 14.35 m²</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — sokl XPS + cihelný obklad</t>
+        </is>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J54" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="50" customHeight="1">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.004</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Špalety EPS</t>
+        </is>
+      </c>
+      <c r="D55" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E55" s="22" t="n">
+        <v>80</v>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>16 oken (DXF) × průměr 5 m obvod špalety = 80.0 bm</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — EPS přesah na špaletách 35-40 mm</t>
+        </is>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J55" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="50" customHeight="1">
+      <c r="A56" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.HSV7.006</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>HSV-7 Fasáda ETICS</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Tenkovrstvá omítka pastovitá</t>
+        </is>
+      </c>
+      <c r="D56" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="n">
+        <v>307.55</v>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
+        <is>
+          <t>ETICS 293.15 m² + sokl 14.4 m² = 307.55 m²</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — pastovitá probarvená lomená bílá</t>
+        </is>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J56" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV71.001</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>PSV-71 Izolace TI</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Podlahový EPS 150</t>
+        </is>
+      </c>
+      <c r="D57" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>124</v>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>1.NP plocha 59.5 m² + 3.NP plocha 64.5 m² = 124.0 m²</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — EPS 150 λ=0.035 tl. 120 mm</t>
+        </is>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J57" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="50" customHeight="1">
+      <c r="A58" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV72.002</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>PSV-72 ZTI</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Nové rozvody vody do 3.NP</t>
+        </is>
+      </c>
+      <c r="D58" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
+        <is>
+          <t>3 koupelen × 15 bm + 2 kuchyně × 8 bm = 61 bm</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — nové koupelny + kuchyně, vyjasnění #6 working assumption</t>
+        </is>
+      </c>
+      <c r="H58" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J58" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="50" customHeight="1">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV72.003</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>PSV-72 ZTI</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Nové odpadní rozvody</t>
+        </is>
+      </c>
+      <c r="D59" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>3 koupelen × 12 bm odpadní + 2 kuchyně × 6 bm = 48 bm</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — nové koupelny + kuchyně, odpad do stávající kanalizace</t>
+        </is>
+      </c>
+      <c r="H59" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J59" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="50" customHeight="1">
+      <c r="A60" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV77.001</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Nášlap vinyl obytné místnosti</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E60" s="22" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
+        <is>
+          <t>Σ obytných místností (vinyl třída) z DXF tabulky místností = 115.4 m²</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 + DXF MTEXT room labels (2× kuchyně, 3× koupelna, 7× chodba)</t>
+        </is>
+      </c>
+      <c r="H60" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J60" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="50" customHeight="1">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV77.002</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Nášlap keramická dlažba</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E61" s="22" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>dlažba (69.7 m²) + dlažba 1.PP technic (32.4 m²) = 102.1 m² mokrých zón</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 + DXF MTEXT room labels</t>
+        </is>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J61" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="50" customHeight="1">
+      <c r="A62" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV77.004</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Betonový potěr s kari nad EPS</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
+        <is>
+          <t>vinyl 115.4 m² + dlažba 69.7 m² = 185.1 m² (mokré skladby kde se klade nový potěr; 1.PP technic vyňato — beton ponechán)</t>
+        </is>
+      </c>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS dům §4 — betonový potěr s kari + samonivelační stěrka</t>
+        </is>
+      </c>
+      <c r="H62" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J62" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="50" customHeight="1">
+      <c r="A63" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum.PSV77.005</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Soklíky podlah</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>vinyl plocha 115.4 m² × 0.42 m soklíku/m² (typ. poměr obvod/plocha RD místnost) = 48.47 bm</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>DXF comprehensive extraction 2026-05-17 | predchozi: TZ ARS — laminátové soklíky standard RD</t>
+        </is>
+      </c>
+      <c r="H63" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J63" s="31" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>